--- a/ru/downloads/data-excel/8.10.2.a.xlsx
+++ b/ru/downloads/data-excel/8.10.2.a.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94866E0F-3A48-4456-B114-E4A311192464}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="сборник (нов)" sheetId="1" r:id="rId1"/>
@@ -62,12 +63,6 @@
     </r>
   </si>
   <si>
-    <t>8.10.2.2 Финансовые показатели страховых компаний</t>
-  </si>
-  <si>
-    <t>8.10.2.2 Financial indicators of insurance companies</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Камсыздандыруу компанияларынын отчёт бергендердин саны </t>
     </r>
@@ -133,22 +128,36 @@
     <t>Items</t>
   </si>
   <si>
-    <t>8.10.2.2 Камсыздандыруу компаниялардын финансылык көрсөткүчтөрү</t>
+    <t>8.10.2.a Камсыздандыруу компаниялардын финансылык көрсөткүчтөрү</t>
+  </si>
+  <si>
+    <t>8.10.2.a Финансовые показатели страховых компаний</t>
+  </si>
+  <si>
+    <t>8.10.2.a Financial indicators of insurance companies</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial Cyr"/>
       <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -244,66 +253,80 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="4">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="4">
-    <cellStyle name="Normal 17" xfId="1"/>
-    <cellStyle name="Normal 2" xfId="3"/>
+  <cellStyles count="5">
+    <cellStyle name="Normal 17" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{6B9C66DE-FFF4-42AB-9688-6ADB99CBF605}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="2"/>
+    <cellStyle name="Обычный 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -580,8 +603,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:R7"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="37.85546875" style="1" customWidth="1"/>
@@ -590,15 +613,15 @@
     <col min="10" max="16384" width="9.28515625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>12</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="D1" s="6"/>
       <c r="E1" s="6"/>
@@ -611,7 +634,7 @@
       <c r="L1" s="6"/>
       <c r="M1" s="6"/>
     </row>
-    <row r="2" spans="1:17" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="15" t="s">
         <v>0</v>
       </c>
@@ -626,16 +649,17 @@
       <c r="K2" s="6"/>
       <c r="L2" s="6"/>
       <c r="M2" s="6"/>
+      <c r="R2" s="17"/>
     </row>
-    <row r="3" spans="1:17" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" s="2" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>9</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>11</v>
       </c>
       <c r="D3" s="8">
         <v>2010</v>
@@ -679,16 +703,19 @@
       <c r="Q3" s="8">
         <v>2023</v>
       </c>
+      <c r="R3" s="18">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:17" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="14" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D4" s="10">
         <v>18</v>
@@ -732,16 +759,19 @@
       <c r="Q4" s="10">
         <v>16</v>
       </c>
+      <c r="R4" s="19">
+        <v>16</v>
+      </c>
     </row>
-    <row r="5" spans="1:17" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="27.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="16" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D5" s="13">
         <v>477.2</v>
@@ -785,8 +815,11 @@
       <c r="Q5" s="13">
         <v>3031.4</v>
       </c>
+      <c r="R5" s="20">
+        <v>5200.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="11"/>
       <c r="C6" s="11"/>
       <c r="D6" s="6"/>
@@ -800,7 +833,7 @@
       <c r="L6" s="6"/>
       <c r="M6" s="6"/>
     </row>
-    <row r="7" spans="1:17" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="6"/>
